--- a/data_extactor/batch_10_fa/trimmed/batch_0033_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0033_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | راهبردهای یادگیری | شنیدن فعال | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | درک مطلب | راهبردهای یادگیری | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | مدیریت و امور اداری | ریاضیات</t>
+          <t>آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران آموزشی دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران دوره ابتدایی، به استثنای آموزش استثنایی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدرسان روان‌شناسی دانشگاهی | مدرسان مددکاری اجتماعی دانشگاهی | دستیاران آموزشی دانشگاهی</t>
+          <t>مدیران آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان روان‌شناسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال</t>
+          <t>درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | خدمات مشتری و شخصی | ارتباطات و رسانه | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان علوم رایانه دانشگاهی | مدرسان علوم تربیتی دانشگاهی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | دستیاران کتابخانه، امور دفتری | کاردان‌ها و تکنسین‌های کتابداری | دستیاران آموزشی دانشگاهی</t>
+          <t>استادان علوم رایانه، آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کمک‌کتابداران دفتری | تکنسین‌های کتابداری | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | حقوق و امور حکومتی | ایمنی و امنیت عمومی | مدیریت و امور اداری | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | قانون و دولت | ایمنی و امنیت عمومی | مدیریت و اداره | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدرسان علوم بازرگانی و مدیریت دانشگاهی | مدرسان علوم تربیتی دانشگاهی | مدرسان حقوق دانشگاهی | مدرسان علوم سیاسی دانشگاهی | مدرسان روان‌شناسی دانشگاهی | مدرسان مددکاری اجتماعی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | مدرسان مددکاری اجتماعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و امور حکومتی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ارتباطات و رسانه</t>
+          <t>قانون و دولت | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدرسان علوم بازرگانی و مدیریت دانشگاهی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی دانشگاهی | مدرسان علوم اقتصادی دانشگاهی | مدرسان تاریخ دانشگاهی | وکلا و مشاوران حقوقی | مدرسان علوم سیاسی دانشگاهی | مدرسان جامعه‌شناسی دانشگاهی</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | وکلا | استادان علوم سیاسی دانشگاه | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | حقوق و امور حکومتی</t>
+          <t>آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدرسان علوم تربیتی دانشگاهی | مشاوران تحصیلی، راهنمایی و شغلی | مدرسان علوم سیاسی دانشگاهی | مدرسان روان‌شناسی دانشگاهی | روان‌شناسان مدرسه | جامعه‌شناسان | مدرسان جامعه‌شناسی دانشگاهی</t>
+          <t>مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | استادان علوم سیاسی دانشگاه | استادان روان‌شناسی دانشگاه | روان‌شناسان مدارس | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | ابتکار | روانی و سیالی ایده‌ها</t>
+          <t>بیان شفاهی | درک کتبی | بیان کتبی | درک شفاهی | وضوح گفتار | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدرسان معماری دانشگاهی | طراحان حرکات موزون و صحنه‌گردانان | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان تاریخ دانشگاهی | رهبران ارکستر و آهنگسازان | مربیان آموزش‌های آزاد و فوق‌برنامه | دستیاران آموزشی دانشگاهی</t>
+          <t>استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | طراحان حرکت و کوروگراف‌ها | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | رهبران ارکستر، مدیران موسیقی و آهنگسازان | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان علوم بازرگانی و مدیریت دانشگاهی | مدرسان علوم تربیتی دانشگاهی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان علوم سیاسی دانشگاهی | مدیران روابط عمومی | مدرسان جامعه‌شناسی دانشگاهی</t>
+          <t>استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | استادان علوم اداری و مدیریت، آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم سیاسی دانشگاه | مدیران روابط عمومی | استادان جامعه‌شناسی دانشگاه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری | شنیدن فعال | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | نگارش | سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان هنرهای تجسمی، نمایشی و موسیقی دانشگاهی | مدرسان علوم ارتباطات دانشگاهی | مدرسان زبان و ادبیات خارجی دانشگاهی | مدرسان تاریخ دانشگاهی | مدرسان فلسفه و الهیات دانشگاهی | مربیان آموزش‌های آزاد و فوق‌برنامه</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مدرسان فلسفه و الهیات در آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان‌های خارجی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>زبان خارجی | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | فلسفه و الهیات | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدرسان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به غیربومیان | مدرسان علوم ارتباطات دانشگاهی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان تاریخ دانشگاهی | مترجمان همزمان و مترجمان متون | مدرسان فلسفه و الهیات دانشگاهی | مربیان آموزش‌های آزاد و فوق‌برنامه</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | مترجمان کتبی و شفاهی | مدرسان فلسفه و الهیات در آموزش عالی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | نگارش | راهبردهای یادگیری | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | نگارش | راهبردهای یادگیری | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | آموزش و پرورش | حقوق و امور حکومتی | جغرافیا | جامعه‌شناسی و انسان‌شناسی | فلسفه و الهیات</t>
+          <t>تاریخ و باستان‌شناسی | آموزش و پرورش | قانون و دولت | جغرافیا | جامعه‌شناسی و انسان‌شناسی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدرسان انسان‌شناسی و باستان‌شناسی دانشگاهی | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاهی | مدرسان زبان و ادبیات انگلیسی دانشگاهی | مدرسان جغرافیا دانشگاهی | تاریخ‌نگاران و پژوهشگران تاریخ | مدرسان فلسفه و الهیات دانشگاهی | مدرسان علوم سیاسی دانشگاهی</t>
+          <t>استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مورخان | مدرسان فلسفه و الهیات در آموزش عالی | استادان علوم سیاسی دانشگاه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
